--- a/artfynd/A 27942-2023 artfynd.xlsx
+++ b/artfynd/A 27942-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27942-2023 artfynd.xlsx
+++ b/artfynd/A 27942-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86710014</v>
+        <v>111333098</v>
       </c>
       <c r="B6" t="n">
-        <v>97848</v>
+        <v>29160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,50 +1177,67 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1888</v>
+        <v>102656</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tofsäxing</t>
+          <t>Hedsidenbi</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Koeleria glauca</t>
+          <t>Colletes fodiens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) DC.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trunelän, mittemot P-platsen, Sk</t>
+          <t>Maglehems naturreservat, Trunelän, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445227.89432473</v>
+        <v>445240.8975562651</v>
       </c>
       <c r="R6" t="n">
-        <v>6181200.311811171</v>
+        <v>6181203.522380427</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1247,7 +1264,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1257,17 +1274,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>300 i vägslänten + ca 100 i gamla grustaget</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,30 +1292,25 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Sandig vägkant + gammalt grustag</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Hans Drake</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Hans Drake</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111333098</v>
+        <v>117203127</v>
       </c>
       <c r="B7" t="n">
-        <v>29160</v>
+        <v>57854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,25 +1319,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102656</v>
+        <v>100010</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hedsidenbi</t>
+          <t>Fältpiplärka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Colletes fodiens</t>
+          <t>Anthus campestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1338,44 +1345,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Maglehems naturreservat, Trunelän, Sk</t>
+          <t>Trunelän, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445240.8975562651</v>
+        <v>445206</v>
       </c>
       <c r="R7" t="n">
-        <v>6181203.522380427</v>
+        <v>6181343</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1399,22 +1389,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Oerhört glädjande att en fältpiplärka hittat platsen redan året efter att tallskogen avverkades i naturvårdssyfte.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,29 +1418,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hans Drake</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hans Drake</t>
+          <t>Ulf Gärdenfors, Martin Stoltze</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117203127</v>
+        <v>117203143</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>57458</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1454,20 +1448,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100010</v>
+        <v>102623</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fältpiplärka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anthus campestris</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1477,14 +1471,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1544,7 +1538,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Oerhört glädjande att en fältpiplärka hittat platsen redan året efter att tallskogen avverkades i naturvårdssyfte.</t>
+          <t>Ev. 9 (3+4+2 där de 3 resp 4 möjligen kan vara samma flock).</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,10 +1565,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117203143</v>
+        <v>118793557</v>
       </c>
       <c r="B9" t="n">
-        <v>57458</v>
+        <v>57387</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1587,35 +1581,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102623</v>
+        <v>102626</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1653,27 +1647,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ev. 9 (3+4+2 där de 3 resp 4 möjligen kan vara samma flock).</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1693,134 +1682,10 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Martin Stoltze</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>118793557</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57387</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>102626</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Törnskata</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lanius collurio</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Trunelän, Sk</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>445206</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6181343</v>
-      </c>
-      <c r="S10" t="n">
-        <v>75</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Kristianstad</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Maglehem</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Ulf Gärdenfors</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Ulf Gärdenfors</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
